--- a/SGC-CKN/Excel/57383178-6c17-44db-a89b-030b58bab82a_Thi_công_cọc_khoan_nhồi__tường_vây_cho_các_hạng_mục_Lô_CT-02_P1-141_D800_31-03-2026.xlsx
+++ b/SGC-CKN/Excel/57383178-6c17-44db-a89b-030b58bab82a_Thi_công_cọc_khoan_nhồi__tường_vây_cho_các_hạng_mục_Lô_CT-02_P1-141_D800_31-03-2026.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="62">
   <si>
     <t>Dự án</t>
   </si>
@@ -38,7 +38,7 @@
     <t>Tên Máy khoan</t>
   </si>
   <si>
-    <t/>
+    <t>SGCT-KCN0003</t>
   </si>
   <si>
     <t>Đường kính</t>
@@ -98,6 +98,9 @@
   <si>
     <t xml:space="preserve">08:50
 31/03/2026</t>
+  </si>
+  <si>
+    <t/>
   </si>
   <si>
     <t>2</t>
@@ -1173,24 +1176,24 @@
         <v>1.23</v>
       </c>
       <c r="K11" s="6" t="s">
-        <v>8</v>
+        <v>28</v>
       </c>
     </row>
     <row r="12" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A12" s="9" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B12" s="9" t="s">
         <v>10</v>
       </c>
       <c r="C12" s="10" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D12" s="11" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E12" s="11" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F12" s="9">
         <v>-1.12</v>
@@ -1208,24 +1211,24 @@
         <v>9.3</v>
       </c>
       <c r="K12" s="10" t="s">
-        <v>8</v>
+        <v>28</v>
       </c>
     </row>
     <row r="13" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A13" s="13" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B13" s="13" t="s">
         <v>10</v>
       </c>
       <c r="C13" s="14" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D13" s="15" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E13" s="15" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F13" s="13">
         <v>-4.22</v>
@@ -1243,24 +1246,24 @@
         <v>4.36</v>
       </c>
       <c r="K13" s="14" t="s">
-        <v>8</v>
+        <v>28</v>
       </c>
     </row>
     <row r="14" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A14" s="16" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B14" s="16" t="s">
         <v>10</v>
       </c>
       <c r="C14" s="17" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D14" s="18" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E14" s="18" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F14" s="16">
         <v>-7.2</v>
@@ -1278,24 +1281,24 @@
         <v>18.87</v>
       </c>
       <c r="K14" s="17" t="s">
-        <v>8</v>
+        <v>28</v>
       </c>
     </row>
     <row r="15" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A15" s="19" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B15" s="19" t="s">
         <v>10</v>
       </c>
       <c r="C15" s="20" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D15" s="21" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E15" s="21" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F15" s="19">
         <v>-16.32</v>
@@ -1313,24 +1316,24 @@
         <v>14.13</v>
       </c>
       <c r="K15" s="20" t="s">
-        <v>8</v>
+        <v>28</v>
       </c>
     </row>
     <row r="16" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A16" s="22" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B16" s="22" t="s">
         <v>10</v>
       </c>
       <c r="C16" s="23" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D16" s="24" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E16" s="24" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F16" s="22">
         <v>-24.56</v>
@@ -1348,24 +1351,24 @@
         <v>0.71</v>
       </c>
       <c r="K16" s="23" t="s">
-        <v>8</v>
+        <v>28</v>
       </c>
     </row>
     <row r="17" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A17" s="26" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B17" s="26" t="s">
         <v>10</v>
       </c>
       <c r="C17" s="27" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D17" s="28" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="E17" s="28" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F17" s="26">
         <v>-25.56</v>
@@ -1383,24 +1386,24 @@
         <v>14.46</v>
       </c>
       <c r="K17" s="27" t="s">
-        <v>8</v>
+        <v>28</v>
       </c>
     </row>
     <row r="18" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A18" s="29" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B18" s="29" t="s">
         <v>10</v>
       </c>
       <c r="C18" s="30" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D18" s="31" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="E18" s="31" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F18" s="29">
         <v>-39.06</v>
@@ -1418,12 +1421,12 @@
         <v>1.27</v>
       </c>
       <c r="K18" s="30" t="s">
-        <v>8</v>
+        <v>28</v>
       </c>
     </row>
     <row r="21" ht="25" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A21" s="32" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B21" s="32"/>
       <c r="C21" s="32"/>
@@ -1529,31 +1532,31 @@
   <sheetData>
     <row r="1" ht="36" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B1" s="3" t="s">
         <v>9</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="H1" s="3" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="I1" s="3" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="2" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1593,7 +1596,7 @@
         <v>10</v>
       </c>
       <c r="C3" s="10" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D3" s="9">
         <v>1</v>
@@ -1622,7 +1625,7 @@
         <v>10</v>
       </c>
       <c r="C4" s="14" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D4" s="13">
         <v>1</v>
@@ -1651,7 +1654,7 @@
         <v>10</v>
       </c>
       <c r="C5" s="17" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D5" s="16">
         <v>1</v>
@@ -1680,7 +1683,7 @@
         <v>10</v>
       </c>
       <c r="C6" s="20" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D6" s="19">
         <v>1</v>
@@ -1709,7 +1712,7 @@
         <v>10</v>
       </c>
       <c r="C7" s="23" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D7" s="22">
         <v>1</v>
@@ -1738,7 +1741,7 @@
         <v>10</v>
       </c>
       <c r="C8" s="27" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D8" s="26">
         <v>1</v>
@@ -1767,7 +1770,7 @@
         <v>10</v>
       </c>
       <c r="C9" s="30" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D9" s="29">
         <v>1</v>
@@ -1790,13 +1793,13 @@
     </row>
     <row r="10" ht="28" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10" s="33" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B10" s="34" t="s">
-        <v>8</v>
+        <v>28</v>
       </c>
       <c r="C10" s="34" t="s">
-        <v>8</v>
+        <v>28</v>
       </c>
       <c r="D10" s="34">
         <v>8</v>

--- a/SGC-CKN/Excel/57383178-6c17-44db-a89b-030b58bab82a_Thi_công_cọc_khoan_nhồi__tường_vây_cho_các_hạng_mục_Lô_CT-02_P1-141_D800_31-03-2026.xlsx
+++ b/SGC-CKN/Excel/57383178-6c17-44db-a89b-030b58bab82a_Thi_công_cọc_khoan_nhồi__tường_vây_cho_các_hạng_mục_Lô_CT-02_P1-141_D800_31-03-2026.xlsx
@@ -215,7 +215,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="16" x14ac:knownFonts="1">
+  <fonts count="15" x14ac:knownFonts="1">
     <font>
       <color theme="1"/>
       <family val="2"/>
@@ -276,12 +276,6 @@
       <name val="Arial"/>
     </font>
     <font>
-      <b/>
-      <color rgb="FFFFFFFF"/>
-      <sz val="10"/>
-      <name val="Arial"/>
-    </font>
-    <font>
       <color rgb="FF7C2D12"/>
       <sz val="10"/>
       <name val="Arial"/>
@@ -304,7 +298,7 @@
       <name val="Arial"/>
     </font>
   </fonts>
-  <fills count="17">
+  <fills count="16">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -364,11 +358,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFD9F99D"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC2626"/>
       </patternFill>
     </fill>
     <fill>
@@ -474,7 +463,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="35">
+  <cellXfs count="34">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -551,6 +540,12 @@
     <xf numFmtId="0" fontId="11" fillId="13" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="11" fillId="13" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="13" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="14" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -560,22 +555,13 @@
     <xf numFmtId="0" fontId="12" fillId="14" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="15" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="15" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="15" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="16" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="15" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="16" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="15" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1304,16 +1290,16 @@
         <v>-16.32</v>
       </c>
       <c r="G15" s="19">
-        <v>-24.56</v>
+        <v>-21.56</v>
       </c>
       <c r="H15" s="19">
         <v>0.58</v>
       </c>
       <c r="I15" s="19">
-        <v>8.24</v>
+        <v>5.24</v>
       </c>
       <c r="J15" s="12">
-        <v>14.13</v>
+        <v>8.98</v>
       </c>
       <c r="K15" s="20" t="s">
         <v>28</v>
@@ -1336,108 +1322,108 @@
         <v>44</v>
       </c>
       <c r="F16" s="22">
-        <v>-24.56</v>
+        <v>-21.56</v>
       </c>
       <c r="G16" s="22">
-        <v>-25.56</v>
+        <v>-25.5</v>
       </c>
       <c r="H16" s="22">
         <v>1.42</v>
       </c>
       <c r="I16" s="22">
-        <v>1</v>
-      </c>
-      <c r="J16" s="25">
-        <v>0.71</v>
+        <v>3.94</v>
+      </c>
+      <c r="J16" s="8">
+        <v>2.78</v>
       </c>
       <c r="K16" s="23" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="17" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A17" s="26" t="s">
+      <c r="A17" s="25" t="s">
         <v>45</v>
       </c>
-      <c r="B17" s="26" t="s">
+      <c r="B17" s="25" t="s">
         <v>10</v>
       </c>
-      <c r="C17" s="27" t="s">
+      <c r="C17" s="26" t="s">
         <v>46</v>
       </c>
-      <c r="D17" s="28" t="s">
+      <c r="D17" s="27" t="s">
         <v>44</v>
       </c>
-      <c r="E17" s="28" t="s">
+      <c r="E17" s="27" t="s">
         <v>47</v>
       </c>
-      <c r="F17" s="26">
-        <v>-25.56</v>
-      </c>
-      <c r="G17" s="26">
+      <c r="F17" s="25">
+        <v>-25.5</v>
+      </c>
+      <c r="G17" s="25">
         <v>-39.06</v>
       </c>
-      <c r="H17" s="26">
+      <c r="H17" s="25">
         <v>0.93</v>
       </c>
-      <c r="I17" s="26">
-        <v>13.5</v>
+      <c r="I17" s="25">
+        <v>13.56</v>
       </c>
       <c r="J17" s="12">
-        <v>14.46</v>
-      </c>
-      <c r="K17" s="27" t="s">
+        <v>14.53</v>
+      </c>
+      <c r="K17" s="26" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="18" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A18" s="29" t="s">
+      <c r="A18" s="28" t="s">
         <v>48</v>
       </c>
-      <c r="B18" s="29" t="s">
+      <c r="B18" s="28" t="s">
         <v>10</v>
       </c>
-      <c r="C18" s="30" t="s">
+      <c r="C18" s="29" t="s">
         <v>49</v>
       </c>
-      <c r="D18" s="31" t="s">
+      <c r="D18" s="30" t="s">
         <v>50</v>
       </c>
-      <c r="E18" s="31" t="s">
+      <c r="E18" s="30" t="s">
         <v>51</v>
       </c>
-      <c r="F18" s="29">
+      <c r="F18" s="28">
         <v>-39.06</v>
       </c>
-      <c r="G18" s="29">
+      <c r="G18" s="28">
         <v>-44.06</v>
       </c>
-      <c r="H18" s="29">
+      <c r="H18" s="28">
         <v>3.93</v>
       </c>
-      <c r="I18" s="29">
+      <c r="I18" s="28">
         <v>5</v>
       </c>
       <c r="J18" s="8">
         <v>1.27</v>
       </c>
-      <c r="K18" s="30" t="s">
+      <c r="K18" s="29" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="21" ht="25" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A21" s="32" t="s">
+      <c r="A21" s="31" t="s">
         <v>52</v>
       </c>
-      <c r="B21" s="32"/>
-      <c r="C21" s="32"/>
-      <c r="D21" s="32"/>
-      <c r="E21" s="32"/>
-      <c r="F21" s="32"/>
-      <c r="G21" s="32"/>
-      <c r="H21" s="32"/>
-      <c r="I21" s="32"/>
-      <c r="J21" s="32"/>
-      <c r="K21" s="32"/>
+      <c r="B21" s="31"/>
+      <c r="C21" s="31"/>
+      <c r="D21" s="31"/>
+      <c r="E21" s="31"/>
+      <c r="F21" s="31"/>
+      <c r="G21" s="31"/>
+      <c r="H21" s="31"/>
+      <c r="I21" s="31"/>
+      <c r="J21" s="31"/>
+      <c r="K21" s="31"/>
     </row>
     <row r="22" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="23" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -1692,16 +1678,16 @@
         <v>-16.32</v>
       </c>
       <c r="F6" s="19">
-        <v>-24.56</v>
+        <v>-21.56</v>
       </c>
       <c r="G6" s="19">
         <v>0.58</v>
       </c>
       <c r="H6" s="19">
-        <v>8.24</v>
+        <v>5.24</v>
       </c>
       <c r="I6" s="12">
-        <v>14.13</v>
+        <v>8.98</v>
       </c>
     </row>
     <row r="7" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1718,73 +1704,73 @@
         <v>1</v>
       </c>
       <c r="E7" s="22">
-        <v>-24.56</v>
+        <v>-21.56</v>
       </c>
       <c r="F7" s="22">
-        <v>-25.56</v>
+        <v>-25.5</v>
       </c>
       <c r="G7" s="22">
         <v>1.42</v>
       </c>
       <c r="H7" s="22">
+        <v>3.94</v>
+      </c>
+      <c r="I7" s="8">
+        <v>2.78</v>
+      </c>
+    </row>
+    <row r="8" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A8" s="25">
+        <v>7</v>
+      </c>
+      <c r="B8" s="25" t="s">
+        <v>10</v>
+      </c>
+      <c r="C8" s="26" t="s">
+        <v>46</v>
+      </c>
+      <c r="D8" s="25">
         <v>1</v>
       </c>
-      <c r="I7" s="25">
-        <v>0.71</v>
-      </c>
-    </row>
-    <row r="8" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A8" s="26">
-        <v>7</v>
-      </c>
-      <c r="B8" s="26" t="s">
+      <c r="E8" s="25">
+        <v>-25.5</v>
+      </c>
+      <c r="F8" s="25">
+        <v>-39.06</v>
+      </c>
+      <c r="G8" s="25">
+        <v>0.93</v>
+      </c>
+      <c r="H8" s="25">
+        <v>13.56</v>
+      </c>
+      <c r="I8" s="12">
+        <v>14.53</v>
+      </c>
+    </row>
+    <row r="9" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A9" s="28">
+        <v>8</v>
+      </c>
+      <c r="B9" s="28" t="s">
         <v>10</v>
       </c>
-      <c r="C8" s="27" t="s">
-        <v>46</v>
-      </c>
-      <c r="D8" s="26">
+      <c r="C9" s="29" t="s">
+        <v>49</v>
+      </c>
+      <c r="D9" s="28">
         <v>1</v>
       </c>
-      <c r="E8" s="26">
-        <v>-25.56</v>
-      </c>
-      <c r="F8" s="26">
+      <c r="E9" s="28">
         <v>-39.06</v>
       </c>
-      <c r="G8" s="26">
-        <v>0.93</v>
-      </c>
-      <c r="H8" s="26">
-        <v>13.5</v>
-      </c>
-      <c r="I8" s="12">
-        <v>14.46</v>
-      </c>
-    </row>
-    <row r="9" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A9" s="29">
-        <v>8</v>
-      </c>
-      <c r="B9" s="29" t="s">
-        <v>10</v>
-      </c>
-      <c r="C9" s="30" t="s">
-        <v>49</v>
-      </c>
-      <c r="D9" s="29">
-        <v>1</v>
-      </c>
-      <c r="E9" s="29">
-        <v>-39.06</v>
-      </c>
-      <c r="F9" s="29">
+      <c r="F9" s="28">
         <v>-44.06</v>
       </c>
-      <c r="G9" s="29">
+      <c r="G9" s="28">
         <v>3.93</v>
       </c>
-      <c r="H9" s="29">
+      <c r="H9" s="28">
         <v>5</v>
       </c>
       <c r="I9" s="8">
@@ -1792,31 +1778,31 @@
       </c>
     </row>
     <row r="10" ht="28" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A10" s="33" t="s">
+      <c r="A10" s="32" t="s">
         <v>61</v>
       </c>
-      <c r="B10" s="34" t="s">
+      <c r="B10" s="33" t="s">
         <v>28</v>
       </c>
-      <c r="C10" s="34" t="s">
+      <c r="C10" s="33" t="s">
         <v>28</v>
       </c>
-      <c r="D10" s="34">
+      <c r="D10" s="33">
         <v>8</v>
       </c>
-      <c r="E10" s="34">
+      <c r="E10" s="33">
         <v>-0.71</v>
       </c>
-      <c r="F10" s="34">
+      <c r="F10" s="33">
         <v>-44.06</v>
       </c>
-      <c r="G10" s="34">
+      <c r="G10" s="33">
         <v>8.7</v>
       </c>
-      <c r="H10" s="34">
+      <c r="H10" s="33">
         <v>43.35</v>
       </c>
-      <c r="I10" s="34">
+      <c r="I10" s="33">
         <v>4.98</v>
       </c>
     </row>
